--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127757530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078967</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857984</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858028</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858056</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198644</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro läns rödlistedatabas</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/229347</t>
         </is>
       </c>
     </row>
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857896</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127109096</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198680</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96601417</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106807772</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857908</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,6 +2304,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858006</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2335,6 +2415,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858033</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2436,6 +2521,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858063</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078671</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2650,6 +2745,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078981</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2751,6 +2851,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198641</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2852,6 +2957,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198651</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2953,6 +3063,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198672</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3062,6 +3177,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127757550</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3169,6 +3289,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078930</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3283,6 +3408,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195266</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3389,6 +3519,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857952</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3490,6 +3625,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198621</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3592,6 +3732,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96601419</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3699,6 +3844,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079581</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3813,6 +3963,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195923</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3918,6 +4073,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103795133</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4024,6 +4184,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858193</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4138,6 +4303,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359762</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4244,6 +4414,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368422</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4346,6 +4521,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80046504</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4452,6 +4632,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151817</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4556,6 +4741,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368660</t>
         </is>
       </c>
     </row>
@@ -4665,6 +4855,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858021</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4767,6 +4962,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858072</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4874,6 +5074,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198647</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4976,6 +5181,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198661</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5082,6 +5292,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368285</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5186,6 +5401,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368286</t>
         </is>
       </c>
     </row>
@@ -5289,6 +5509,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857910</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5390,6 +5615,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198629</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5499,6 +5729,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391590</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5604,6 +5839,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112271059</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5705,6 +5945,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198756</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5811,6 +6056,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858061</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5912,6 +6162,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198671</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6013,6 +6268,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857925</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6119,6 +6379,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858034</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6220,6 +6485,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858074</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6321,6 +6591,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198626</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6422,6 +6697,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198643</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6528,6 +6808,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210289</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6634,6 +6919,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368591</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6741,6 +7031,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078649</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6860,6 +7155,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900403</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6957,6 +7257,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73691143</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7058,6 +7363,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733752</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7164,6 +7474,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151679</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7278,6 +7593,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96334081</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7384,6 +7704,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359789</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7485,6 +7810,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858054</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7586,6 +7916,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198646</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7692,6 +8027,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857920</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7798,6 +8138,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858048</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7899,6 +8244,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198645</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8001,6 +8351,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80046502</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8107,6 +8462,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368201</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8213,6 +8573,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368202</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8317,6 +8682,11 @@
       <c r="AY74" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368203</t>
         </is>
       </c>
     </row>
@@ -8425,6 +8795,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198632</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8526,6 +8901,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198659</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8627,6 +9007,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198667</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8731,6 +9116,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368723</t>
         </is>
       </c>
     </row>
@@ -8839,6 +9229,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858018</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8943,6 +9338,11 @@
       <c r="AY80" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368341</t>
         </is>
       </c>
     </row>
@@ -9046,6 +9446,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858050</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9151,6 +9556,11 @@
       <c r="AY82" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151498</t>
         </is>
       </c>
     </row>
@@ -9259,6 +9669,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195240</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9373,6 +9788,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195935</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9479,6 +9899,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359793</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9580,6 +10005,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858029</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9681,6 +10111,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858049</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9788,6 +10223,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078655</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9895,6 +10335,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078988</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9996,6 +10441,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198622</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10097,6 +10547,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198682</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10206,6 +10661,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391581</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10307,6 +10767,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858070</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10408,6 +10873,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198683</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10524,6 +10994,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12692</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10633,6 +11108,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96601406</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10752,6 +11232,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128090297</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10858,6 +11343,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87880231</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10969,6 +11459,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900407</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11073,6 +11568,11 @@
       <c r="AY100" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151816</t>
         </is>
       </c>
     </row>
@@ -11182,6 +11682,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195962</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11284,6 +11789,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858066</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11395,6 +11905,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900406</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11497,6 +12012,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80046503</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11603,6 +12123,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368447</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11704,6 +12229,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733782</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11818,6 +12348,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195231</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11919,6 +12454,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198743</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12020,6 +12560,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198755</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12126,6 +12671,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857904</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12233,6 +12783,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078934</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12347,6 +12902,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359797</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12458,8 +13018,127 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>97948</v>
+        <v>97949</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97905</v>
+        <v>97906</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136103383</v>
       </c>
       <c r="B89" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10574,7 +10574,7 @@
         <v>136103380</v>
       </c>
       <c r="B91" t="n">
-        <v>91550</v>
+        <v>91551</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -12014,7 +12014,7 @@
         <v>136103331</v>
       </c>
       <c r="B104" t="n">
-        <v>93398</v>
+        <v>93399</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>136106499</v>
       </c>
       <c r="B107" t="n">
-        <v>75416</v>
+        <v>75417</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136107535</v>
       </c>
       <c r="B108" t="n">
-        <v>75416</v>
+        <v>75417</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>136107679</v>
       </c>
       <c r="B109" t="n">
-        <v>75416</v>
+        <v>75417</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>136106670</v>
       </c>
       <c r="B114" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>136106545</v>
       </c>
       <c r="B115" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136106660</v>
       </c>
       <c r="B116" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>136103300</v>
       </c>
       <c r="B118" t="n">
-        <v>107003</v>
+        <v>107005</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>136106552</v>
       </c>
       <c r="B119" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>136106673</v>
       </c>
       <c r="B120" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136107698</v>
       </c>
       <c r="B121" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>136103391</v>
       </c>
       <c r="B123" t="n">
-        <v>106467</v>
+        <v>106469</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14403,7 +14403,7 @@
         <v>136107643</v>
       </c>
       <c r="B124" t="n">
-        <v>106467</v>
+        <v>106469</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>136103972</v>
       </c>
       <c r="B125" t="n">
-        <v>100054</v>
+        <v>100056</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136106473</v>
       </c>
       <c r="B126" t="n">
-        <v>100054</v>
+        <v>100056</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>136107586</v>
       </c>
       <c r="B127" t="n">
-        <v>100054</v>
+        <v>100056</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>136103341</v>
       </c>
       <c r="B132" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>136104024</v>
       </c>
       <c r="B133" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136106482</v>
       </c>
       <c r="B134" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>136106695</v>
       </c>
       <c r="B135" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>136107556</v>
       </c>
       <c r="B136" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>136106667</v>
       </c>
       <c r="B138" t="n">
-        <v>101423</v>
+        <v>101425</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>136107703</v>
       </c>
       <c r="B139" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>136107647</v>
       </c>
       <c r="B140" t="n">
-        <v>99602</v>
+        <v>99603</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>136103347</v>
       </c>
       <c r="B141" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136107617</v>
       </c>
       <c r="B142" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>136104021</v>
       </c>
       <c r="B152" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>136107324</v>
       </c>
       <c r="B153" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>

--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>97949</v>
+        <v>97950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97906</v>
+        <v>97907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98017</v>
+        <v>98018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136103383</v>
       </c>
       <c r="B89" t="n">
-        <v>93392</v>
+        <v>93393</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136103380</v>
       </c>
       <c r="B91" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>136103331</v>
       </c>
       <c r="B104" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>136106670</v>
       </c>
       <c r="B114" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>136106545</v>
       </c>
       <c r="B115" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136106660</v>
       </c>
       <c r="B116" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>136103300</v>
       </c>
       <c r="B118" t="n">
-        <v>107005</v>
+        <v>107006</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>136106552</v>
       </c>
       <c r="B119" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>136106673</v>
       </c>
       <c r="B120" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136107698</v>
       </c>
       <c r="B121" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>136103391</v>
       </c>
       <c r="B123" t="n">
-        <v>106469</v>
+        <v>106470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>136107643</v>
       </c>
       <c r="B124" t="n">
-        <v>106469</v>
+        <v>106470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>136103972</v>
       </c>
       <c r="B125" t="n">
-        <v>100056</v>
+        <v>100057</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136106473</v>
       </c>
       <c r="B126" t="n">
-        <v>100056</v>
+        <v>100057</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>136107586</v>
       </c>
       <c r="B127" t="n">
-        <v>100056</v>
+        <v>100057</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>136103341</v>
       </c>
       <c r="B132" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>136104024</v>
       </c>
       <c r="B133" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136106482</v>
       </c>
       <c r="B134" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>136106695</v>
       </c>
       <c r="B135" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>136107556</v>
       </c>
       <c r="B136" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>136106667</v>
       </c>
       <c r="B138" t="n">
-        <v>101425</v>
+        <v>101426</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>136107703</v>
       </c>
       <c r="B139" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>136107647</v>
       </c>
       <c r="B140" t="n">
-        <v>99603</v>
+        <v>99604</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>136103347</v>
       </c>
       <c r="B141" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136107617</v>
       </c>
       <c r="B142" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>136104021</v>
       </c>
       <c r="B152" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>136107324</v>
       </c>
       <c r="B153" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>97950</v>
+        <v>97951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>97908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98018</v>
+        <v>98019</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136103383</v>
       </c>
       <c r="B89" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136103380</v>
       </c>
       <c r="B91" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>136103331</v>
       </c>
       <c r="B104" t="n">
-        <v>93400</v>
+        <v>93401</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>136106499</v>
       </c>
       <c r="B107" t="n">
-        <v>75417</v>
+        <v>75418</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136107535</v>
       </c>
       <c r="B108" t="n">
-        <v>75417</v>
+        <v>75418</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>136107679</v>
       </c>
       <c r="B109" t="n">
-        <v>75417</v>
+        <v>75418</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>136106670</v>
       </c>
       <c r="B114" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13380,7 +13380,7 @@
         <v>136106545</v>
       </c>
       <c r="B115" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136106660</v>
       </c>
       <c r="B116" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13723,7 +13723,7 @@
         <v>136103300</v>
       </c>
       <c r="B118" t="n">
-        <v>107006</v>
+        <v>107007</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>136106552</v>
       </c>
       <c r="B119" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>136106673</v>
       </c>
       <c r="B120" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14059,7 +14059,7 @@
         <v>136107698</v>
       </c>
       <c r="B121" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>136103391</v>
       </c>
       <c r="B123" t="n">
-        <v>106470</v>
+        <v>106471</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>136107643</v>
       </c>
       <c r="B124" t="n">
-        <v>106470</v>
+        <v>106471</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>136103972</v>
       </c>
       <c r="B125" t="n">
-        <v>100057</v>
+        <v>100058</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136106473</v>
       </c>
       <c r="B126" t="n">
-        <v>100057</v>
+        <v>100058</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>136107586</v>
       </c>
       <c r="B127" t="n">
-        <v>100057</v>
+        <v>100058</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15334,7 +15334,7 @@
         <v>136103341</v>
       </c>
       <c r="B132" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>136104024</v>
       </c>
       <c r="B133" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136106482</v>
       </c>
       <c r="B134" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>136106695</v>
       </c>
       <c r="B135" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>136107556</v>
       </c>
       <c r="B136" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>136106667</v>
       </c>
       <c r="B138" t="n">
-        <v>101426</v>
+        <v>101427</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16146,7 +16146,7 @@
         <v>136107703</v>
       </c>
       <c r="B139" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>136107647</v>
       </c>
       <c r="B140" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>136103347</v>
       </c>
       <c r="B141" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136107617</v>
       </c>
       <c r="B142" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>136104021</v>
       </c>
       <c r="B152" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>136107324</v>
       </c>
       <c r="B153" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93367</v>
+        <v>93373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>97951</v>
+        <v>97957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97908</v>
+        <v>97914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98019</v>
+        <v>98025</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136103383</v>
       </c>
       <c r="B89" t="n">
-        <v>93394</v>
+        <v>93400</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136103380</v>
       </c>
       <c r="B91" t="n">
-        <v>91553</v>
+        <v>91559</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>136103331</v>
       </c>
       <c r="B104" t="n">
-        <v>93401</v>
+        <v>93407</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>136106499</v>
       </c>
       <c r="B107" t="n">
-        <v>75418</v>
+        <v>75422</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136107535</v>
       </c>
       <c r="B108" t="n">
-        <v>75418</v>
+        <v>75422</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>136107679</v>
       </c>
       <c r="B109" t="n">
-        <v>75418</v>
+        <v>75422</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>136106670</v>
       </c>
       <c r="B114" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13380,7 +13380,7 @@
         <v>136106545</v>
       </c>
       <c r="B115" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136106660</v>
       </c>
       <c r="B116" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13723,7 +13723,7 @@
         <v>136103300</v>
       </c>
       <c r="B118" t="n">
-        <v>107007</v>
+        <v>107013</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>136106552</v>
       </c>
       <c r="B119" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>136106673</v>
       </c>
       <c r="B120" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14059,7 +14059,7 @@
         <v>136107698</v>
       </c>
       <c r="B121" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>136103391</v>
       </c>
       <c r="B123" t="n">
-        <v>106471</v>
+        <v>106477</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>136107643</v>
       </c>
       <c r="B124" t="n">
-        <v>106471</v>
+        <v>106477</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>136103972</v>
       </c>
       <c r="B125" t="n">
-        <v>100058</v>
+        <v>100064</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136106473</v>
       </c>
       <c r="B126" t="n">
-        <v>100058</v>
+        <v>100064</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>136107586</v>
       </c>
       <c r="B127" t="n">
-        <v>100058</v>
+        <v>100064</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15334,7 +15334,7 @@
         <v>136103341</v>
       </c>
       <c r="B132" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>136104024</v>
       </c>
       <c r="B133" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136106482</v>
       </c>
       <c r="B134" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>136106695</v>
       </c>
       <c r="B135" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>136107556</v>
       </c>
       <c r="B136" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>136106667</v>
       </c>
       <c r="B138" t="n">
-        <v>101427</v>
+        <v>101433</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16146,7 +16146,7 @@
         <v>136107703</v>
       </c>
       <c r="B139" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>136107647</v>
       </c>
       <c r="B140" t="n">
-        <v>99605</v>
+        <v>99611</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>136103347</v>
       </c>
       <c r="B141" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136107617</v>
       </c>
       <c r="B142" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>136104021</v>
       </c>
       <c r="B152" t="n">
-        <v>93368</v>
+        <v>93374</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>136107324</v>
       </c>
       <c r="B153" t="n">
-        <v>93368</v>
+        <v>93374</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 63194-2025 artfynd.xlsx
+++ b/artfynd/A 63194-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93373</v>
+        <v>93374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>97957</v>
+        <v>97958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97914</v>
+        <v>97915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98025</v>
+        <v>98026</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>136103383</v>
       </c>
       <c r="B89" t="n">
-        <v>93400</v>
+        <v>93401</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>136103380</v>
       </c>
       <c r="B91" t="n">
-        <v>91559</v>
+        <v>91560</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>136103331</v>
       </c>
       <c r="B104" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>136106499</v>
       </c>
       <c r="B107" t="n">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136107535</v>
       </c>
       <c r="B108" t="n">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>136107679</v>
       </c>
       <c r="B109" t="n">
-        <v>75422</v>
+        <v>75423</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>136106670</v>
       </c>
       <c r="B114" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>136106545</v>
       </c>
       <c r="B115" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136106660</v>
       </c>
       <c r="B116" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>136103300</v>
       </c>
       <c r="B118" t="n">
-        <v>107013</v>
+        <v>107014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>136106552</v>
       </c>
       <c r="B119" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>136106673</v>
       </c>
       <c r="B120" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>136107698</v>
       </c>
       <c r="B121" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>136103391</v>
       </c>
       <c r="B123" t="n">
-        <v>106477</v>
+        <v>106478</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>136107643</v>
       </c>
       <c r="B124" t="n">
-        <v>106477</v>
+        <v>106478</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>136103972</v>
       </c>
       <c r="B125" t="n">
-        <v>100064</v>
+        <v>100065</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136106473</v>
       </c>
       <c r="B126" t="n">
-        <v>100064</v>
+        <v>100065</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>136107586</v>
       </c>
       <c r="B127" t="n">
-        <v>100064</v>
+        <v>100065</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>136103341</v>
       </c>
       <c r="B132" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>136104024</v>
       </c>
       <c r="B133" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136106482</v>
       </c>
       <c r="B134" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>136106695</v>
       </c>
       <c r="B135" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>136107556</v>
       </c>
       <c r="B136" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>136106667</v>
       </c>
       <c r="B138" t="n">
-        <v>101433</v>
+        <v>101434</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>136107703</v>
       </c>
       <c r="B139" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>136107647</v>
       </c>
       <c r="B140" t="n">
-        <v>99611</v>
+        <v>99612</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>136103347</v>
       </c>
       <c r="B141" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136107617</v>
       </c>
       <c r="B142" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>136104021</v>
       </c>
       <c r="B152" t="n">
-        <v>93374</v>
+        <v>93375</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>136107324</v>
       </c>
       <c r="B153" t="n">
-        <v>93374</v>
+        <v>93375</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
